--- a/data/trans_orig/Q5415-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5415-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2007</t>
+          <t>Población según si es capaz de salir a caminar en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1169</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>14,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1169</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6706</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6370</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1169</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5282</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11406</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4639</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>27005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34491</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>25906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>36760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57166</t>
+          <t>56265</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69014</t>
+          <t>68731</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6076</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60578</t>
+          <t>60534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79799</t>
+          <t>79856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92697</t>
+          <t>92889</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143002</t>
+          <t>143961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157569</t>
+          <t>158095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>2933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44023</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64634</t>
+          <t>64914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>77321</t>
+          <t>77276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112794</t>
+          <t>112691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126954</t>
+          <t>126804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>16640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49110</t>
+          <t>49723</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54460</t>
+          <t>55178</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67039</t>
+          <t>67867</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106457</t>
+          <t>107011</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120806</t>
+          <t>121218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1861</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1672</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>13546</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>28581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50756</t>
+          <t>51642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63398</t>
+          <t>63843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -3013,97 +3013,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7863</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3,59%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>2522</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>8503</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>9093</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>7701</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>14889</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20698</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>39634</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>46245</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52072</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64756</t>
+          <t>64529</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>93223</t>
+          <t>95823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>109487</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8910</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11244</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>3692</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92159</t>
+          <t>92864</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102377</t>
+          <t>102657</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>98885</t>
+          <t>98789</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>112074</t>
+          <t>111834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>196312</t>
+          <t>197731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>212040</t>
+          <t>212868</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>16403</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5993</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>16353</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3464</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>15956</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10662</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>92343</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>105243</t>
+          <t>104900</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>126808</t>
+          <t>127445</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>142945</t>
+          <t>142865</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>223673</t>
+          <t>223343</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>244909</t>
+          <t>245219</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14168</t>
+          <t>13688</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20501</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>42942</t>
+          <t>43824</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>53037</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>21587</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>69914</t>
+          <t>69606</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>67918</t>
+          <t>67379</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>104490</t>
+          <t>102809</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>452714</t>
+          <t>452426</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>474734</t>
+          <t>474765</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>573141</t>
+          <t>573959</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>609438</t>
+          <t>608800</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1035031</t>
+          <t>1036994</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1077761</t>
+          <t>1078503</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2012</t>
+          <t>Población según si es capaz de salir a caminar en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4410</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>18725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35201</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43313</t>
+          <t>43256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23519</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37304</t>
+          <t>37213</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61850</t>
+          <t>63038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78509</t>
+          <t>79543</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33052</t>
+          <t>31331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12153</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24983</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59781</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74676</t>
+          <t>74107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68393</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86515</t>
+          <t>85559</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132337</t>
+          <t>133836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156625</t>
+          <t>157135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18348</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>4150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>55488</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70144</t>
+          <t>70192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102567</t>
+          <t>102314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120635</t>
+          <t>120110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20275</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>50265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60856</t>
+          <t>60758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>66820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>79269</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120556</t>
+          <t>121093</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137948</t>
+          <t>137760</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13751</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22213</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30500</t>
+          <t>30513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35553</t>
+          <t>35768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>46022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61174</t>
+          <t>61526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74861</t>
+          <t>75347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3158</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13724</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16836</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37943</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48525</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>48886</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61699</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91129</t>
+          <t>91614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108459</t>
+          <t>108107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,64%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>14006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,12 +7824,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>24871</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15123</t>
+          <t>14951</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>37659</t>
+          <t>37573</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90356</t>
+          <t>90489</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>106262</t>
+          <t>105987</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>102940</t>
+          <t>102978</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>122644</t>
+          <t>122977</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>200492</t>
+          <t>200308</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>224601</t>
+          <t>224937</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>17902</t>
+          <t>18055</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>11330</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>6661</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>21429</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>26886</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>108027</t>
+          <t>107738</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118590</t>
+          <t>118604</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>131133</t>
+          <t>132440</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>149970</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>246419</t>
+          <t>244815</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>266629</t>
+          <t>266273</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35080</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>54309</t>
+          <t>54820</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>89035</t>
+          <t>86674</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>76081</t>
+          <t>73900</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>114411</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49502</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>57764</t>
+          <t>58899</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>90451</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>90432</t>
+          <t>91036</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>131499</t>
+          <t>131923</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>483320</t>
+          <t>483955</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>514973</t>
+          <t>514056</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>576082</t>
+          <t>577264</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>621151</t>
+          <t>620995</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1074094</t>
+          <t>1070977</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1125241</t>
+          <t>1125797</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,43%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2016</t>
+          <t>Población según si es capaz de salir a caminar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,97 +9413,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6314</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>12,78%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1126</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5576</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5844</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21475</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32530</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>65047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80966</t>
+          <t>80408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22677</t>
+          <t>23696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10456</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28806</t>
+          <t>26902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>78173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85824</t>
+          <t>85808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87030</t>
+          <t>85720</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103965</t>
+          <t>103774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167199</t>
+          <t>167820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187858</t>
+          <t>188011</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10345,7 +10345,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54016</t>
+          <t>53830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62017</t>
+          <t>61972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66903</t>
+          <t>66921</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123637</t>
+          <t>125254</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138412</t>
+          <t>138761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>12886</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>13607</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55107</t>
+          <t>54993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63030</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71328</t>
+          <t>72375</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>86569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131020</t>
+          <t>131232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147778</t>
+          <t>147319</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -11237,97 +11237,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1676</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2318</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7107</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>7099</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2318</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>8186</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>817</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7535</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>21081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>26100</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>41263</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26674</t>
+          <t>27252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41557</t>
+          <t>41233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64243</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80745</t>
+          <t>81000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13225</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>36071</t>
+          <t>35914</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>45172</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>49855</t>
+          <t>49519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61590</t>
+          <t>61782</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89631</t>
+          <t>89894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>105370</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,97%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33756</t>
+          <t>33407</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33434</t>
+          <t>34115</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41156</t>
+          <t>41476</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92434</t>
+          <t>91823</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105453</t>
+          <t>105302</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>96639</t>
+          <t>97203</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>119795</t>
+          <t>119788</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>194053</t>
+          <t>194660</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>222363</t>
+          <t>220998</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>14737</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>27847</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11575</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29995</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,26%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>117379</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>129825</t>
+          <t>129677</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>147441</t>
+          <t>146962</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>166905</t>
+          <t>166595</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>271461</t>
+          <t>271656</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>292887</t>
+          <t>292587</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27509</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>56057</t>
+          <t>57206</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44815</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>75923</t>
+          <t>77370</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>40089</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>70333</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>108314</t>
+          <t>108757</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>96106</t>
+          <t>97923</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>139683</t>
+          <t>140756</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>531103</t>
+          <t>531396</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>555099</t>
+          <t>555910</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>624085</t>
+          <t>624004</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>670383</t>
+          <t>670012</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1164826</t>
+          <t>1164210</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1217009</t>
+          <t>1216266</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de salir a caminar en 2023</t>
+          <t>Población según si es capaz de salir a caminar en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>403</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9249</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51515</t>
+          <t>51273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54027</t>
+          <t>53945</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61087</t>
+          <t>61217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>108506</t>
+          <t>108478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116536</t>
+          <t>116527</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20072</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26837</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12831</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25262</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>30324</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65585</t>
+          <t>65811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76405</t>
+          <t>76316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88277</t>
+          <t>87457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103250</t>
+          <t>103390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>158693</t>
+          <t>158796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>177012</t>
+          <t>177622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,93%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>16035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>23254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21098</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>34936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51606</t>
+          <t>51491</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62544</t>
+          <t>62494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56914</t>
+          <t>56766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69545</t>
+          <t>68883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111452</t>
+          <t>112008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>128179</t>
+          <t>128350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,76%</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7550</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15692</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8649</t>
+          <t>8258</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>17311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>63526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71811</t>
+          <t>71628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76528</t>
+          <t>76013</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>86676</t>
+          <t>87052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143488</t>
+          <t>144225</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156622</t>
+          <t>156862</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3566</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15662,12 +15662,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14785</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>26344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32225</t>
+          <t>32268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42947</t>
+          <t>43327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50386</t>
+          <t>50655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71700</t>
+          <t>71992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>81086</t>
+          <t>81679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>13888</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9883</t>
+          <t>9789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46325</t>
+          <t>46174</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53850</t>
+          <t>53371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50918</t>
+          <t>50713</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>91166</t>
+          <t>91462</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41431</t>
+          <t>41720</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>34725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2329</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>43420</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>43237</t>
+          <t>42027</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>107890</t>
+          <t>108440</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>119048</t>
+          <t>118987</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>257996</t>
+          <t>257003</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>331441</t>
+          <t>331110</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>385733</t>
+          <t>388587</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>449089</t>
+          <t>449256</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15872</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>15746</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>25814</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>40957</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34151</t>
+          <t>35462</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>52466</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>130209</t>
+          <t>130171</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>140316</t>
+          <t>140199</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>134949</t>
+          <t>134537</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>150795</t>
+          <t>151938</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>269109</t>
+          <t>268718</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>290162</t>
+          <t>288845</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,55%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15089</t>
+          <t>14018</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>28645</t>
+          <t>28746</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>38425</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>91213</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>60481</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>109030</t>
+          <t>109599</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>35187</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>57670</t>
+          <t>56521</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>64041</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>151635</t>
+          <t>150500</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>105578</t>
+          <t>106753</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>192158</t>
+          <t>190979</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>570957</t>
+          <t>570107</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>595510</t>
+          <t>595297</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>794833</t>
+          <t>793464</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>934241</t>
+          <t>928126</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1387129</t>
+          <t>1387219</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1515594</t>
+          <t>1516315</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
